--- a/Ecommerce_Dashboard.xlsx
+++ b/Ecommerce_Dashboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhin\OneDrive\Desktop\Data Analytics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhin\OneDrive\Desktop\Data Analytics\Indian E-Commerce Sales Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC3E6CA-70F7-4861-BCA1-7CE24307EA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A3A8DB-CFB9-40AA-98FE-E972C08BEBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FA114D4D-8A45-4CAC-B495-F07891FBDAC8}"/>
   </bookViews>
@@ -37,36 +37,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="86">
   <si>
-    <t>beleza_saude</t>
-  </si>
-  <si>
-    <t>relogios_presentes</t>
-  </si>
-  <si>
-    <t>esporte_lazer</t>
-  </si>
-  <si>
-    <t>cama_mesa_banho</t>
-  </si>
-  <si>
-    <t>informatica_acessorios</t>
-  </si>
-  <si>
-    <t>moveis_decoracao</t>
-  </si>
-  <si>
-    <t>utilidades_domesticas</t>
-  </si>
-  <si>
-    <t>cool_stuff</t>
-  </si>
-  <si>
-    <t>automotivo</t>
-  </si>
-  <si>
-    <t>brinquedos</t>
-  </si>
-  <si>
     <t>product_category_name</t>
   </si>
   <si>
@@ -178,75 +148,6 @@
     <t>total_orders</t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>RJ</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>CE</t>
-  </si>
-  <si>
-    <t>RS</t>
-  </si>
-  <si>
-    <t>PR</t>
-  </si>
-  <si>
-    <t>BA</t>
-  </si>
-  <si>
-    <t>TO</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>SE</t>
-  </si>
-  <si>
-    <t>GO</t>
-  </si>
-  <si>
-    <t>MT</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>DF</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>PB</t>
-  </si>
-  <si>
-    <t>ES</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>RN</t>
-  </si>
-  <si>
-    <t>RO</t>
-  </si>
-  <si>
     <t>customer_state</t>
   </si>
   <si>
@@ -277,9 +178,6 @@
     <t>percentage</t>
   </si>
   <si>
-    <t>E-Commerce Sales Analysis Dashboard</t>
-  </si>
-  <si>
     <t>Average Order Value</t>
   </si>
   <si>
@@ -289,10 +187,112 @@
     <t>Total Orders</t>
   </si>
   <si>
-    <t>Tools Used: MySQL, Excel</t>
-  </si>
-  <si>
-    <t>Dataset: Olist Brazilian E-Commerce Dataset (20,000 Orders Sample)</t>
+    <t>Maharashtra</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
+    <t>Tamil Nadu</t>
+  </si>
+  <si>
+    <t>Kerala</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Gujarat</t>
+  </si>
+  <si>
+    <t>Telangana</t>
+  </si>
+  <si>
+    <t>Uttar Pradesh</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t>Andhra Pradesh</t>
+  </si>
+  <si>
+    <t>Delhi NCR</t>
+  </si>
+  <si>
+    <t>Punjab</t>
+  </si>
+  <si>
+    <t>Haryana</t>
+  </si>
+  <si>
+    <t>Rajasthan</t>
+  </si>
+  <si>
+    <t>Assam</t>
+  </si>
+  <si>
+    <t>Odisha</t>
+  </si>
+  <si>
+    <t>Bihar</t>
+  </si>
+  <si>
+    <t>Jharkhand</t>
+  </si>
+  <si>
+    <t>Madhya Pradesh</t>
+  </si>
+  <si>
+    <t>Chhattisgarh</t>
+  </si>
+  <si>
+    <t>West Bengal</t>
+  </si>
+  <si>
+    <t>Uttarakhand</t>
+  </si>
+  <si>
+    <t>Himachal Pradesh</t>
+  </si>
+  <si>
+    <t>Health &amp; Beauty</t>
+  </si>
+  <si>
+    <t>Watches &amp; Gifts</t>
+  </si>
+  <si>
+    <t>Sports &amp; Leisure</t>
+  </si>
+  <si>
+    <t>Home &amp; Bedding</t>
+  </si>
+  <si>
+    <t>Electronics &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Furniture &amp; Decor</t>
+  </si>
+  <si>
+    <t>Home Essentials</t>
+  </si>
+  <si>
+    <t>Lifestyle Products</t>
+  </si>
+  <si>
+    <t>Automotive</t>
+  </si>
+  <si>
+    <t>Toys</t>
+  </si>
+  <si>
+    <t>Dataset: Public E-Commerce Dataset adapted for an Indian business scenario</t>
+  </si>
+  <si>
+    <t>Indian E-Commerce Sales Dashboard</t>
+  </si>
+  <si>
+    <t>Tools Used: SQL(MySQL), Excel</t>
   </si>
 </sst>
 </file>
@@ -446,13 +446,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="8" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -467,30 +485,18 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF9BC2E6"/>
+      <color rgb="FF000000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -616,34 +622,34 @@
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>beleza_saude</c:v>
+                  <c:v>Health &amp; Beauty</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>relogios_presentes</c:v>
+                  <c:v>Watches &amp; Gifts</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>esporte_lazer</c:v>
+                  <c:v>Sports &amp; Leisure</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>cama_mesa_banho</c:v>
+                  <c:v>Home &amp; Bedding</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>informatica_acessorios</c:v>
+                  <c:v>Electronics &amp; Accessories</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>moveis_decoracao</c:v>
+                  <c:v>Furniture &amp; Decor</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>utilidades_domesticas</c:v>
+                  <c:v>Home Essentials</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>cool_stuff</c:v>
+                  <c:v>Lifestyle Products</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>automotivo</c:v>
+                  <c:v>Automotive</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>brinquedos</c:v>
+                  <c:v>Toys</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -708,7 +714,7 @@
       <c:catAx>
         <c:axId val="322009711"/>
         <c:scaling>
-          <c:orientation val="minMax"/>
+          <c:orientation val="maxMin"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -762,7 +768,7 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="t"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -830,10 +836,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="accent1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -1258,10 +1261,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="accent1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -1469,73 +1469,73 @@
               <c:strCache>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
-                  <c:v>SP</c:v>
+                  <c:v>Maharashtra</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>RJ</c:v>
+                  <c:v>Karnataka</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>MG</c:v>
+                  <c:v>Tamil Nadu</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>SC</c:v>
+                  <c:v>Kerala</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>CE</c:v>
+                  <c:v>Delhi</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>RS</c:v>
+                  <c:v>Gujarat</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>PR</c:v>
+                  <c:v>Telangana</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>BA</c:v>
+                  <c:v>Uttar Pradesh</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>TO</c:v>
+                  <c:v>Goa</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>MA</c:v>
+                  <c:v>Andhra Pradesh</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>SE</c:v>
+                  <c:v>Delhi NCR</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>GO</c:v>
+                  <c:v>Punjab</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>MT</c:v>
+                  <c:v>Haryana</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>MS</c:v>
+                  <c:v>Rajasthan</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>DF</c:v>
+                  <c:v>Assam</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>PE</c:v>
+                  <c:v>Odisha</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>PA</c:v>
+                  <c:v>Bihar</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>PB</c:v>
+                  <c:v>Jharkhand</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>ES</c:v>
+                  <c:v>Madhya Pradesh</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>AL</c:v>
+                  <c:v>Chhattisgarh</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>AM</c:v>
+                  <c:v>West Bengal</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>RN</c:v>
+                  <c:v>Uttarakhand</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>RO</c:v>
+                  <c:v>Himachal Pradesh</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1639,7 +1639,7 @@
       <c:catAx>
         <c:axId val="387147935"/>
         <c:scaling>
-          <c:orientation val="minMax"/>
+          <c:orientation val="maxMin"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1693,7 +1693,7 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="t"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -2295,7 +2295,7 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
         <c:firstSliceAng val="0"/>
         <c:holeSize val="75"/>
@@ -2356,10 +2356,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="accent1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -4048,13 +4045,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>218209</xdr:colOff>
+      <xdr:colOff>218208</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>119842</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>540327</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>361949</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>138545</xdr:rowOff>
     </xdr:to>
@@ -4086,15 +4083,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>221673</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>69273</xdr:rowOff>
+      <xdr:colOff>545522</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>435033</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>153093</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4124,13 +4121,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>201583</xdr:colOff>
+      <xdr:colOff>201582</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>128154</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>540327</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>400049</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>166254</xdr:rowOff>
     </xdr:to>
@@ -4162,15 +4159,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>261158</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>35329</xdr:rowOff>
+      <xdr:colOff>565959</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>130578</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>498763</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>124691</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4503,33 +4500,33 @@
     <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1">
         <v>137822.28</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1">
         <v>13440</v>
@@ -4537,125 +4534,125 @@
     </row>
     <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="B3" s="1">
         <v>113703.37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F3" s="1">
         <v>11805</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
+      <c r="A4" t="s">
+        <v>75</v>
       </c>
       <c r="B4" s="1">
         <v>101166.46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1">
         <v>11631.3</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
+      <c r="A5" t="s">
+        <v>76</v>
       </c>
       <c r="B5" s="1">
         <v>97031.07</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1">
         <v>8399.9699999999993</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
+      <c r="A6" t="s">
+        <v>77</v>
       </c>
       <c r="B6" s="1">
         <v>94385.16</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F6" s="1">
         <v>8148</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
+      <c r="A7" t="s">
+        <v>78</v>
       </c>
       <c r="B7" s="1">
         <v>88016.45</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F7" s="1">
         <v>8009.73</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
+      <c r="A8" t="s">
+        <v>79</v>
       </c>
       <c r="B8" s="1">
         <v>80542.570000000007</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1">
         <v>7287.2</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
+      <c r="A9" t="s">
+        <v>80</v>
       </c>
       <c r="B9" s="1">
         <v>62545.77</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1">
         <v>6735</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
+      <c r="A10" t="s">
+        <v>81</v>
       </c>
       <c r="B10" s="1">
         <v>56175.55</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1">
         <v>6428.7</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
+      <c r="A11" t="s">
+        <v>82</v>
       </c>
       <c r="B11" s="1">
         <v>53129.09</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1">
         <v>6295.8</v>
@@ -4663,27 +4660,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1">
         <v>3</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F21" s="1">
         <v>39453.58</v>
@@ -4691,13 +4688,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B22" s="1">
         <v>61</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>48</v>
+      <c r="E22" t="s">
+        <v>51</v>
       </c>
       <c r="F22" s="1">
         <v>28645.03</v>
@@ -4705,13 +4702,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B23" s="1">
         <v>175</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>49</v>
+      <c r="E23" t="s">
+        <v>52</v>
       </c>
       <c r="F23" s="1">
         <v>11754.82</v>
@@ -4719,13 +4716,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B24" s="1">
         <v>350</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>50</v>
+      <c r="E24" t="s">
+        <v>53</v>
       </c>
       <c r="F24" s="1">
         <v>8786.35</v>
@@ -4733,13 +4730,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B25" s="1">
         <v>559</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>51</v>
+      <c r="E25" t="s">
+        <v>54</v>
       </c>
       <c r="F25" s="1">
         <v>4233.83</v>
@@ -4747,13 +4744,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1">
         <v>469</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>52</v>
+      <c r="E26" t="s">
+        <v>55</v>
       </c>
       <c r="F26" s="1">
         <v>3633.82</v>
@@ -4761,13 +4758,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B27" s="1">
         <v>752</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>53</v>
+      <c r="E27" t="s">
+        <v>56</v>
       </c>
       <c r="F27" s="1">
         <v>3423.25</v>
@@ -4775,13 +4772,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B28" s="1">
         <v>642</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>54</v>
+      <c r="E28" t="s">
+        <v>57</v>
       </c>
       <c r="F28" s="1">
         <v>2859.1</v>
@@ -4789,13 +4786,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B29" s="1">
         <v>797</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>55</v>
+      <c r="E29" t="s">
+        <v>58</v>
       </c>
       <c r="F29" s="1">
         <v>2779.93</v>
@@ -4803,13 +4800,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B30" s="1">
         <v>904</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>56</v>
+      <c r="E30" t="s">
+        <v>59</v>
       </c>
       <c r="F30" s="1">
         <v>1631.16</v>
@@ -4817,13 +4814,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B31" s="1">
         <v>843</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>57</v>
+      <c r="E31" t="s">
+        <v>60</v>
       </c>
       <c r="F31" s="1">
         <v>1543.9</v>
@@ -4831,13 +4828,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B32" s="1">
         <v>889</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F32" s="1">
         <v>1390.36</v>
@@ -4845,13 +4842,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B33" s="1">
         <v>1569</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>59</v>
+      <c r="E33" t="s">
+        <v>62</v>
       </c>
       <c r="F33" s="1">
         <v>1301.57</v>
@@ -4859,13 +4856,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B34" s="1">
         <v>1136</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>60</v>
+      <c r="E34" t="s">
+        <v>63</v>
       </c>
       <c r="F34" s="1">
         <v>1027.99</v>
@@ -4873,13 +4870,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B35" s="1">
         <v>1451</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F35" s="1">
         <v>936.6</v>
@@ -4887,13 +4884,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B36" s="1">
         <v>1385</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F36" s="1">
         <v>876.77</v>
@@ -4901,13 +4898,13 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B37" s="1">
         <v>1443</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>63</v>
+      <c r="E37" t="s">
+        <v>66</v>
       </c>
       <c r="F37" s="1">
         <v>710.69</v>
@@ -4915,13 +4912,13 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B38" s="1">
         <v>1360</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F38" s="1">
         <v>648.9</v>
@@ -4929,13 +4926,13 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B39" s="1">
         <v>1391</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F39" s="1">
         <v>377.8</v>
@@ -4943,13 +4940,13 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B40" s="1">
         <v>1215</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>66</v>
+      <c r="E40" t="s">
+        <v>69</v>
       </c>
       <c r="F40" s="1">
         <v>285.29000000000002</v>
@@ -4957,13 +4954,13 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B41" s="1">
         <v>1266</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>67</v>
+      <c r="E41" t="s">
+        <v>70</v>
       </c>
       <c r="F41" s="1">
         <v>214.9</v>
@@ -4971,13 +4968,13 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B42" s="1">
         <v>1336</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>68</v>
+      <c r="E42" t="s">
+        <v>71</v>
       </c>
       <c r="F42" s="1">
         <v>159.97999999999999</v>
@@ -4986,8 +4983,8 @@
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
-      <c r="E43" s="1" t="s">
-        <v>69</v>
+      <c r="E43" t="s">
+        <v>72</v>
       </c>
       <c r="F43" s="1">
         <v>49.9</v>
@@ -4995,18 +4992,18 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" t="s">
         <v>46</v>
-      </c>
-      <c r="C50" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B51" s="1">
         <v>19430</v>
@@ -5017,7 +5014,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="B52" s="1">
         <v>215</v>
@@ -5028,7 +5025,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="B53" s="1">
         <v>124</v>
@@ -5039,7 +5036,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="B54" s="1">
         <v>117</v>
@@ -5050,7 +5047,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="B55" s="1">
         <v>57</v>
@@ -5061,7 +5058,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="B56" s="1">
         <v>55</v>
@@ -5072,7 +5069,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="B57" s="1">
         <v>2</v>
@@ -5082,6 +5079,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B11">
+    <sortCondition descending="1" ref="B2:B11"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5098,36 +5098,36 @@
     <col min="11" max="11" width="19.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+    <row r="1" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -5149,77 +5149,77 @@
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:27" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A4" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="15"/>
+      <c r="A4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15"/>
+      <c r="E4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="15"/>
+      <c r="I4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="K4" s="10"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
     </row>
     <row r="5" spans="1:27" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A5" s="16"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="13"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="8"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="13"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="8"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:27" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A6" s="6">
+      <c r="A6" s="14">
         <v>241356.29</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="12">
+      <c r="E6" s="18">
         <v>20000</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="6">
+      <c r="I6" s="14">
         <v>137.55000000000001</v>
       </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="8"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="13"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
     <row r="7" spans="1:27" ht="31.8" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="17"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="11"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="17"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -5853,7 +5853,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -5871,7 +5871,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>

--- a/Ecommerce_Dashboard.xlsx
+++ b/Ecommerce_Dashboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhin\OneDrive\Desktop\Data Analytics\Indian E-Commerce Sales Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhin\OneDrive\Desktop\Data Analytics\Indian E-Commerce Sales Analysis\ecommerce-sales-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A3A8DB-CFB9-40AA-98FE-E972C08BEBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{842A5956-DDEA-4EAE-952B-48BB5DF4C40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FA114D4D-8A45-4CAC-B495-F07891FBDAC8}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="107">
   <si>
     <t>product_category_name</t>
   </si>
@@ -286,13 +286,76 @@
     <t>Toys</t>
   </si>
   <si>
-    <t>Dataset: Public E-Commerce Dataset adapted for an Indian business scenario</t>
-  </si>
-  <si>
     <t>Indian E-Commerce Sales Dashboard</t>
   </si>
   <si>
-    <t>Tools Used: SQL(MySQL), Excel</t>
+    <t>revenue_percentage</t>
+  </si>
+  <si>
+    <t>beleza_saude</t>
+  </si>
+  <si>
+    <t>relogios_presentes</t>
+  </si>
+  <si>
+    <t>esporte_lazer</t>
+  </si>
+  <si>
+    <t>cama_mesa_banho</t>
+  </si>
+  <si>
+    <t>informatica_acessorios</t>
+  </si>
+  <si>
+    <t>moveis_decoracao</t>
+  </si>
+  <si>
+    <t>utilidades_domesticas</t>
+  </si>
+  <si>
+    <t>cool_stuff</t>
+  </si>
+  <si>
+    <t>automotivo</t>
+  </si>
+  <si>
+    <t>brinquedos</t>
+  </si>
+  <si>
+    <t>monthly_revenue</t>
+  </si>
+  <si>
+    <t>average_order_value</t>
+  </si>
+  <si>
+    <t>Tools : MySQL | Excel</t>
+  </si>
+  <si>
+    <t>Dataset : Public E-Commerce Dataset adapted for an Indian business scenario</t>
+  </si>
+  <si>
+    <t>Jammu &amp; Kashmir</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Revenue</t>
   </si>
 </sst>
 </file>
@@ -302,7 +365,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,8 +389,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -336,7 +414,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor rgb="FF9BC2E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,23 +517,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -461,6 +538,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -473,6 +551,9 @@
     <xf numFmtId="8" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -482,9 +563,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,8 +580,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF000000"/>
       <color rgb="FF9BC2E6"/>
-      <color rgb="FF000000"/>
     </mruColors>
   </colors>
   <extLst>
@@ -542,7 +629,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>Top Categories by Revenue</a:t>
             </a:r>
           </a:p>
@@ -740,7 +827,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -894,7 +981,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
+              <a:rPr lang="en-IN" b="1"/>
               <a:t>Monthly Order Trend</a:t>
             </a:r>
           </a:p>
@@ -1217,7 +1304,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1319,7 +1406,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
+              <a:rPr lang="en-IN" b="1"/>
               <a:t>Revenue by State</a:t>
             </a:r>
           </a:p>
@@ -1665,7 +1752,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1800,7 +1887,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
+              <a:rPr lang="en-IN" b="1"/>
               <a:t>Order Status Distribution</a:t>
             </a:r>
           </a:p>
@@ -2323,7 +2410,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2357,6 +2444,330 @@
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="accent1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Revenue by Region</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis_Data!$B$102</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis_Data!$A$103:$A$107</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Central</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis_Data!$B$103:$B$107</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>45077.77</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42491.37</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19170.689999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8306.32</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1679.37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DCF1-4B59-BC73-03812AD4F411}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="610565039"/>
+        <c:axId val="610565519"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="610565039"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="610565519"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="610565519"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="610565039"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -2500,6 +2911,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
@@ -4040,20 +4491,525 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>218208</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>119842</xdr:rowOff>
+      <xdr:colOff>234371</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>361949</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>138545</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>184727</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>55418</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4082,16 +5038,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>545522</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>323272</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>11546</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>190499</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>152399</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>4619</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4121,15 +5077,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>201582</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>128154</xdr:rowOff>
+      <xdr:colOff>205046</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18472</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>400049</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>166254</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4158,16 +5114,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>565959</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>130578</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>388158</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>32326</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>190501</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>60036</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4189,6 +5145,329 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>396240</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50A42EAF-B361-E62F-D3E2-F5A05A9E9A6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9324340" y="10416540"/>
+          <a:ext cx="7683500" cy="2293620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="600"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>KEY BUSINESS INSIGHTS</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="342900" indent="-342900" algn="l">
+            <a:buFont typeface="Wingdings" panose="05000000000000000000" pitchFamily="2" charset="2"/>
+            <a:buChar char="ü"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>Health &amp; Beauty generated the highest revenue.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="342900" indent="-342900" algn="l">
+            <a:buFont typeface="Wingdings" panose="05000000000000000000" pitchFamily="2" charset="2"/>
+            <a:buChar char="ü"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>Maharashtra contributed the highest revenue.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="342900" indent="-342900" algn="l">
+            <a:buFont typeface="Wingdings" panose="05000000000000000000" pitchFamily="2" charset="2"/>
+            <a:buChar char="ü"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2000"/>
+            <a:t>West and South regions generated the highest overall revenue.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="2000" b="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="342900" indent="-342900" algn="l">
+            <a:buFont typeface="Wingdings" panose="05000000000000000000" pitchFamily="2" charset="2"/>
+            <a:buChar char="ü"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>Monthly orders increased steadily.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="342900" indent="-342900" algn="l">
+            <a:buFont typeface="Wingdings" panose="05000000000000000000" pitchFamily="2" charset="2"/>
+            <a:buChar char="ü"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2000" b="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>Over 97% of orders were delivered successfully</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2000" b="0">
+              <a:latin typeface="+mn-lt"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>386426</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>32558</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>396240</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>32559</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{962F6516-80E3-B2D6-C9BC-7317CC459140}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9317066" y="12956078"/>
+          <a:ext cx="7690774" cy="2011681"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:spcAft>
+              <a:spcPts val="600"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2400" b="1"/>
+            <a:t>BUSINESS RECOMMENDATIONS</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="342900" indent="-342900">
+            <a:buFont typeface="Wingdings" panose="05000000000000000000" pitchFamily="2" charset="2"/>
+            <a:buChar char="ü"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2000"/>
+            <a:t>Increase inventory for top-performing categories.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="342900" indent="-342900">
+            <a:buFont typeface="Wingdings" panose="05000000000000000000" pitchFamily="2" charset="2"/>
+            <a:buChar char="ü"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2000"/>
+            <a:t>Expand marketing in lower-performing states.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="342900" indent="-342900">
+            <a:buFont typeface="Wingdings" panose="05000000000000000000" pitchFamily="2" charset="2"/>
+            <a:buChar char="ü"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2000"/>
+            <a:t>Prepare inventory before peak sales months.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="342900" indent="-342900">
+            <a:buFont typeface="Wingdings" panose="05000000000000000000" pitchFamily="2" charset="2"/>
+            <a:buChar char="ü"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IN" sz="2000"/>
+            <a:t>Maintain high order fulfillment efficiency.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABAA5A30-27CA-41E2-B5BA-8821C073B09A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4494,14 +5773,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE66E5D3-40EF-4FA6-8EE0-83A7620BE3F6}">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:R107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -4990,7 +6273,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>45</v>
       </c>
@@ -5000,8 +6283,26 @@
       <c r="C50" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E50" t="s">
+        <v>0</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>84</v>
+      </c>
+      <c r="I50" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K50" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>38</v>
       </c>
@@ -5011,8 +6312,27 @@
       <c r="C51" s="1">
         <v>97.15</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E51" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51" s="1">
+        <v>137822.28</v>
+      </c>
+      <c r="G51" s="1">
+        <v>5.71</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J51" s="1">
+        <v>39453.58</v>
+      </c>
+      <c r="K51" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="M51" s="1"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>39</v>
       </c>
@@ -5022,8 +6342,27 @@
       <c r="C52" s="1">
         <v>1.08</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E52" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F52" s="1">
+        <v>113703.37</v>
+      </c>
+      <c r="G52" s="1">
+        <v>4.71</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J52" s="1">
+        <v>28645.03</v>
+      </c>
+      <c r="K52" s="1">
+        <v>1.19</v>
+      </c>
+      <c r="M52" s="1"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>40</v>
       </c>
@@ -5033,8 +6372,27 @@
       <c r="C53" s="1">
         <v>0.62</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E53" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F53" s="1">
+        <v>101166.46</v>
+      </c>
+      <c r="G53" s="1">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J53" s="1">
+        <v>11754.82</v>
+      </c>
+      <c r="K53" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="M53" s="1"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>41</v>
       </c>
@@ -5044,8 +6402,27 @@
       <c r="C54" s="1">
         <v>0.59</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E54" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F54" s="1">
+        <v>97031.07</v>
+      </c>
+      <c r="G54" s="1">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J54" s="1">
+        <v>8786.35</v>
+      </c>
+      <c r="K54" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="M54" s="1"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>42</v>
       </c>
@@ -5055,8 +6432,27 @@
       <c r="C55" s="1">
         <v>0.28999999999999998</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E55" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" s="1">
+        <v>94385.16</v>
+      </c>
+      <c r="G55" s="1">
+        <v>3.91</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J55" s="1">
+        <v>4233.83</v>
+      </c>
+      <c r="K55" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="M55" s="1"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>43</v>
       </c>
@@ -5066,8 +6462,27 @@
       <c r="C56" s="1">
         <v>0.28000000000000003</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E56" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F56" s="1">
+        <v>88016.45</v>
+      </c>
+      <c r="G56" s="1">
+        <v>3.65</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J56" s="1">
+        <v>3633.82</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="M56" s="1"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>44</v>
       </c>
@@ -5076,6 +6491,661 @@
       </c>
       <c r="C57" s="1">
         <v>0.01</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F57" s="1">
+        <v>80542.570000000007</v>
+      </c>
+      <c r="G57" s="1">
+        <v>3.34</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J57" s="1">
+        <v>3423.25</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M57" s="1"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E58" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F58" s="1">
+        <v>62545.77</v>
+      </c>
+      <c r="G58" s="1">
+        <v>2.59</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J58" s="1">
+        <v>2859.1</v>
+      </c>
+      <c r="K58" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="M58" s="1"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E59" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F59" s="1">
+        <v>56175.55</v>
+      </c>
+      <c r="G59" s="1">
+        <v>2.33</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J59" s="1">
+        <v>2779.93</v>
+      </c>
+      <c r="K59" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="M59" s="1"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E60" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" s="1">
+        <v>53129.09</v>
+      </c>
+      <c r="G60" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1631.16</v>
+      </c>
+      <c r="K60" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M60" s="1"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I61" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1543.9</v>
+      </c>
+      <c r="K61" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="M61" s="1"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I62" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J62" s="1">
+        <v>1390.36</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="M62" s="1"/>
+    </row>
+    <row r="63" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I63" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1301.57</v>
+      </c>
+      <c r="K63" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="M63" s="1"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I64" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1027.99</v>
+      </c>
+      <c r="K64" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="M64" s="1"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I65" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J65" s="1">
+        <v>936.6</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="M65" s="1"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I66" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J66" s="1">
+        <v>876.77</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="M66" s="1"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J67" s="1">
+        <v>710.69</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="M67" s="1"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I68" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J68" s="1">
+        <v>648.9</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="M68" s="1"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I69" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J69" s="1">
+        <v>377.8</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="M69" s="1"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I70" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J70" s="1">
+        <v>285.29000000000002</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="M70" s="1"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I71" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J71" s="1">
+        <v>214.9</v>
+      </c>
+      <c r="K71" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="M71" s="1"/>
+    </row>
+    <row r="72" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I72" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J72" s="1">
+        <v>159.97999999999999</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="M72" s="1"/>
+    </row>
+    <row r="73" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I73" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J73" s="1">
+        <v>49.9</v>
+      </c>
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>35</v>
+      </c>
+      <c r="B75" t="s">
+        <v>95</v>
+      </c>
+      <c r="E75" t="s">
+        <v>37</v>
+      </c>
+      <c r="F75" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" s="1">
+        <v>1232.58</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F76" s="1">
+        <v>1389.96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" s="1">
+        <v>5854.72</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F77" s="1">
+        <v>514.63</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B78" s="1">
+        <v>7087.02</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F78" s="1">
+        <v>324.45</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B79" s="1">
+        <v>14810.91</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F79" s="1">
+        <v>260.41000000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B80" s="1">
+        <v>9534.64</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F80" s="1">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" s="1">
+        <v>20141.099999999999</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F81" s="1">
+        <v>222.83</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B82" s="1">
+        <v>21041.68</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F82" s="1">
+        <v>191.01</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B83" s="1">
+        <v>15792.83</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F83" s="1">
+        <v>181.24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="1">
+        <v>23583.59</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F84" s="1">
+        <v>162.69999999999999</v>
+      </c>
+      <c r="R84" s="1"/>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B85" s="1">
+        <v>31932.42</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F85" s="1">
+        <v>126.4</v>
+      </c>
+      <c r="R85" s="1"/>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B86" s="1">
+        <v>28355.06</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F86" s="1">
+        <v>107.45</v>
+      </c>
+      <c r="R86" s="1"/>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" s="1">
+        <v>35754.86</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F87" s="1">
+        <v>105.77</v>
+      </c>
+      <c r="R87" s="1"/>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B88" s="1">
+        <v>25310.45</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F88" s="1">
+        <v>104.07</v>
+      </c>
+      <c r="R88" s="1"/>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B89" s="1">
+        <v>30711.43</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F89" s="1">
+        <v>103.82</v>
+      </c>
+      <c r="R89" s="1"/>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B90" s="1">
+        <v>30060.41</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F90" s="1">
+        <v>97.42</v>
+      </c>
+      <c r="R90" s="1"/>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B91" s="1">
+        <v>36608.21</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F91" s="1">
+        <v>95.1</v>
+      </c>
+      <c r="R91" s="1"/>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B92" s="1">
+        <v>42987.71</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F92" s="1">
+        <v>94.45</v>
+      </c>
+      <c r="R92" s="1"/>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B93" s="1">
+        <v>37437.94</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F93" s="1">
+        <v>92.69</v>
+      </c>
+      <c r="R93" s="1"/>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B94" s="1">
+        <v>29336.18</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F94" s="1">
+        <v>92.52</v>
+      </c>
+      <c r="R94" s="1"/>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B95" s="1">
+        <v>33107.24</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F95" s="1">
+        <v>92.23</v>
+      </c>
+      <c r="R95" s="1"/>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B96" s="1">
+        <v>26194.93</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F96" s="1">
+        <v>79.989999999999995</v>
+      </c>
+      <c r="R96" s="1"/>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="E97" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F97" s="1">
+        <v>78.97</v>
+      </c>
+      <c r="R97" s="1"/>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="E98" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F98" s="1">
+        <v>49.9</v>
+      </c>
+      <c r="R98" s="1"/>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R99" s="1"/>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R100" s="1"/>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R101" s="1"/>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>105</v>
+      </c>
+      <c r="B102" t="s">
+        <v>106</v>
+      </c>
+      <c r="C102" t="s">
+        <v>84</v>
+      </c>
+      <c r="R102" s="1"/>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B103" s="1">
+        <v>45077.77</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1.87</v>
+      </c>
+      <c r="R103" s="1"/>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B104" s="1">
+        <v>42491.37</v>
+      </c>
+      <c r="C104" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="R104" s="1"/>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B105" s="1">
+        <v>19170.689999999999</v>
+      </c>
+      <c r="C105" s="1">
+        <v>0.79</v>
+      </c>
+      <c r="R105" s="1"/>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B106" s="1">
+        <v>8306.32</v>
+      </c>
+      <c r="C106" s="1">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B107" s="1">
+        <v>1679.37</v>
+      </c>
+      <c r="C107" s="1">
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5088,864 +7158,2332 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC6231A-0F8E-4842-9E7E-6BF9B4861D7D}">
-  <dimension ref="A1:AA51"/>
+  <dimension ref="A1:AA86"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
     <col min="9" max="9" width="11.77734375" customWidth="1"/>
     <col min="11" max="11" width="19.77734375" customWidth="1"/>
+    <col min="16" max="16" width="7.5546875" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="30.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="A1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+    </row>
+    <row r="2" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
     </row>
     <row r="3" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
     </row>
     <row r="4" spans="1:27" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="6"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="8" t="s">
+      <c r="L4" s="6"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
     </row>
     <row r="5" spans="1:27" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
     </row>
     <row r="6" spans="1:27" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A6" s="14">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="12">
         <v>241356.29</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="18">
+      <c r="F6" s="10"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="13">
         <v>20000</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="14">
+      <c r="L6" s="10"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="12">
         <v>137.55000000000001</v>
       </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="1:27" ht="31.8" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="R7" s="5"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="R8" s="5"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="AA9" s="5"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="AA9" s="2"/>
     </row>
     <row r="10" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+      <c r="Y27" s="3"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+      <c r="Y29" s="3"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+      <c r="Y31" s="3"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
+      <c r="W35" s="3"/>
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3"/>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="3"/>
+      <c r="X37" s="3"/>
+      <c r="Y37" s="3"/>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3"/>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="3"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
+      <c r="W43" s="3"/>
+      <c r="X43" s="3"/>
+      <c r="Y43" s="3"/>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3"/>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="3"/>
+      <c r="V45" s="3"/>
+      <c r="W45" s="3"/>
+      <c r="X45" s="3"/>
+      <c r="Y45" s="3"/>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+      <c r="S47" s="3"/>
+      <c r="T47" s="3"/>
+      <c r="U47" s="3"/>
+      <c r="V47" s="3"/>
+      <c r="W47" s="3"/>
+      <c r="X47" s="3"/>
+      <c r="Y47" s="3"/>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
+      <c r="X48" s="3"/>
+      <c r="Y48" s="3"/>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="S49" s="3"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="3"/>
+      <c r="X49" s="3"/>
+      <c r="Y49" s="3"/>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3"/>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3"/>
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="3"/>
+      <c r="X51" s="3"/>
+      <c r="Y51" s="3"/>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3"/>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+      <c r="S53" s="3"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="3"/>
+      <c r="V53" s="3"/>
+      <c r="W53" s="3"/>
+      <c r="X53" s="3"/>
+      <c r="Y53" s="3"/>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3"/>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3"/>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+      <c r="T59" s="3"/>
+      <c r="U59" s="3"/>
+      <c r="V59" s="3"/>
+      <c r="W59" s="3"/>
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3"/>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="3"/>
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="V63" s="3"/>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="3"/>
+      <c r="T65" s="3"/>
+      <c r="U65" s="3"/>
+      <c r="V65" s="3"/>
+      <c r="W65" s="3"/>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="3"/>
+      <c r="S69" s="3"/>
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69" s="3"/>
+      <c r="W69" s="3"/>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="3"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="3"/>
+      <c r="S71" s="3"/>
+      <c r="T71" s="3"/>
+      <c r="U71" s="3"/>
+      <c r="V71" s="3"/>
+      <c r="W71" s="3"/>
+      <c r="X71" s="3"/>
+      <c r="Y71" s="3"/>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="3"/>
+      <c r="S73" s="3"/>
+      <c r="T73" s="3"/>
+      <c r="U73" s="3"/>
+      <c r="V73" s="3"/>
+      <c r="W73" s="3"/>
+      <c r="X73" s="3"/>
+      <c r="Y73" s="3"/>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="3"/>
+      <c r="S75" s="3"/>
+      <c r="T75" s="3"/>
+      <c r="U75" s="3"/>
+      <c r="V75" s="3"/>
+      <c r="W75" s="3"/>
+      <c r="X75" s="3"/>
+      <c r="Y75" s="3"/>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3"/>
+      <c r="Q77" s="3"/>
+      <c r="R77" s="3"/>
+      <c r="S77" s="3"/>
+      <c r="T77" s="3"/>
+      <c r="U77" s="3"/>
+      <c r="V77" s="3"/>
+      <c r="W77" s="3"/>
+      <c r="X77" s="3"/>
+      <c r="Y77" s="3"/>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3"/>
+      <c r="S78" s="3"/>
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
+      <c r="X78" s="3"/>
+      <c r="Y78" s="3"/>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3"/>
+      <c r="Q79" s="3"/>
+      <c r="R79" s="3"/>
+      <c r="S79" s="3"/>
+      <c r="T79" s="3"/>
+      <c r="U79" s="3"/>
+      <c r="V79" s="3"/>
+      <c r="W79" s="3"/>
+      <c r="X79" s="3"/>
+      <c r="Y79" s="3"/>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3"/>
+      <c r="S80" s="3"/>
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3"/>
+    </row>
+    <row r="81" spans="1:26" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A81" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B81" s="21"/>
+      <c r="C81" s="21"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="21"/>
+      <c r="I81" s="21"/>
+      <c r="J81" s="21"/>
+      <c r="K81" s="21"/>
+      <c r="L81" s="21"/>
+      <c r="M81" s="21"/>
+      <c r="N81" s="21"/>
+      <c r="O81" s="21"/>
+      <c r="P81" s="21"/>
+      <c r="Q81" s="21"/>
+      <c r="R81" s="3"/>
+      <c r="S81" s="3"/>
+      <c r="T81" s="3"/>
+      <c r="U81" s="3"/>
+      <c r="V81" s="3"/>
+      <c r="W81" s="3"/>
+      <c r="X81" s="3"/>
+      <c r="Y81" s="3"/>
+    </row>
+    <row r="82" spans="1:26" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A82" s="20"/>
+      <c r="B82" s="21"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="21"/>
+      <c r="J82" s="21"/>
+      <c r="K82" s="21"/>
+      <c r="L82" s="21"/>
+      <c r="M82" s="21"/>
+      <c r="N82" s="21"/>
+      <c r="O82" s="21"/>
+      <c r="P82" s="21"/>
+      <c r="Q82" s="21"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="1:26" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="A83" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83" s="21"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="21"/>
+      <c r="H83" s="21"/>
+      <c r="I83" s="21"/>
+      <c r="J83" s="21"/>
+      <c r="K83" s="21"/>
+      <c r="L83" s="21"/>
+      <c r="M83" s="21"/>
+      <c r="N83" s="21"/>
+      <c r="O83" s="21"/>
+      <c r="P83" s="21"/>
+      <c r="Q83" s="21"/>
+      <c r="R83" s="3"/>
+      <c r="S83" s="3"/>
+      <c r="T83" s="3"/>
+      <c r="U83" s="3"/>
+      <c r="V83" s="3"/>
+      <c r="W83" s="3"/>
+      <c r="X83" s="3"/>
+      <c r="Y83" s="3"/>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3"/>
+      <c r="S84" s="3"/>
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="V85" s="19"/>
+      <c r="W85" s="19"/>
+      <c r="X85" s="19"/>
+      <c r="Y85" s="19"/>
+      <c r="Z85" s="19"/>
+    </row>
+    <row r="86" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="V86" s="19"/>
+      <c r="W86" s="19"/>
+      <c r="X86" s="19"/>
+      <c r="Y86" s="19"/>
+      <c r="Z86" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="A4:C5"/>
-    <mergeCell ref="A6:C7"/>
     <mergeCell ref="E4:G5"/>
     <mergeCell ref="E6:G7"/>
-    <mergeCell ref="I4:K5"/>
-    <mergeCell ref="I6:K7"/>
+    <mergeCell ref="K4:M5"/>
+    <mergeCell ref="K6:M7"/>
+    <mergeCell ref="Q4:S5"/>
+    <mergeCell ref="Q6:S7"/>
+    <mergeCell ref="A1:V2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>